--- a/MSA_PDB/pdb70_220313_db.xlsx
+++ b/MSA_PDB/pdb70_220313_db.xlsx
@@ -949,6 +949,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -970,6 +971,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1032,15 +1034,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1050,9 +1043,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M119"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="4.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3.51"/>
@@ -2824,44 +2817,44 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+    <row r="44" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="1" t="n">
         <v>0.236</v>
       </c>
-      <c r="D44" s="0" t="n">
+      <c r="D44" s="1" t="n">
         <v>470</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="1" t="n">
         <v>325</v>
       </c>
-      <c r="F44" s="0" t="n">
+      <c r="F44" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="G44" s="0" t="n">
+      <c r="G44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="0" t="n">
+      <c r="H44" s="1" t="n">
         <v>449</v>
       </c>
-      <c r="I44" s="0" t="n">
+      <c r="I44" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="0" t="n">
+      <c r="J44" s="1" t="n">
         <v>461</v>
       </c>
-      <c r="K44" s="0" t="n">
+      <c r="K44" s="1" t="n">
         <v>1.916E-078</v>
       </c>
-      <c r="L44" s="0" t="n">
+      <c r="L44" s="1" t="n">
         <v>271</v>
       </c>
-      <c r="M44" s="0" t="s">
+      <c r="M44" s="1" t="s">
         <v>116</v>
       </c>
     </row>
